--- a/mode_docx_gen/pmi_dzt/kzt2_modes/КЦТ_1.xlsx
+++ b/mode_docx_gen/pmi_dzt/kzt2_modes/КЦТ_1.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -460,6 +460,8 @@
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="20" customWidth="1" min="21" max="21"/>
     <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,85 +492,95 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>ksch3_tdif</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>comp3i0_rmxu1_tdif</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>comp3i0_rmxu2_tdif</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>comp3i0_rmxu3_tdif</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SGF1_rctr1_ctr</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>SGF2_rctr1_ctr</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>SGF1_rctr2_ctr</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>SGF2_rctr2_ctr</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>SGF1_rctr3_ctr</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SGF2_rctr3_ctr</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>SGF1_pdif1_tdif</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>SGF2_pdif1_tdif</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>SGF3_pdif1_tdif</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>SGF1_pdif2_tdif</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SGF1_hf2phar1_tdif</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SGF1_hf5phar1_tdif</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>SGF1_rctr1_tdif</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>SGF1_ptrc1_tprmofflvlgc</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>SGF1_rbre1_tprmofflvlgc</t>
         </is>
@@ -602,30 +614,30 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -635,10 +647,16 @@
       <c r="T2" t="n">
         <v>0</v>
       </c>
-      <c r="U2" s="2" t="n">
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="X2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -653,7 +671,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT2"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -702,6 +720,11 @@
     <col width="20" customWidth="1" min="44" max="44"/>
     <col width="20" customWidth="1" min="45" max="45"/>
     <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="20" customWidth="1" min="47" max="47"/>
+    <col width="20" customWidth="1" min="48" max="48"/>
+    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="20" customWidth="1" min="50" max="50"/>
+    <col width="20" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -812,125 +835,150 @@
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>Ubaz_rmxu3_tdif</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>Iperv_rmxu1_tdif</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Iperv_rmxu2_tdif</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Iperv_rmxu3_tdif</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Inomterm_rmxu1_tdif</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Inomterm_rmxu2_tdif</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Inomterm_rmxu3_tdif</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Ivtor_rmxu1_tdif</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Ivtor_rmxu2_tdif</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Ivtor_rmxu3_tdif</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Nsch_rmxu1_tdif</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Nsch_rmxu2_tdif</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Nsch_rmxu3_tdif</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>T1_pdif1_tdif</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Isr_pdif1_tdif</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Isrzagrub_pdif1_tdif</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>It1_pdif1_tdif</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>It2_pdif1_tdif</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Kt1_pdif1_tdif</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Kt2_pdif1_tdif</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>T1_pdif2_tdif</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Iset_pdif2_tdif</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>T1_hf2phar1_tdif</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>T2_hf2phar1_tdif</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Ratio_hf2phar1_tdif</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>T1_hf5phar1_tdif</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>T2_hf5phar1_tdif</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>Ratio_hf5phar1_tdif</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>T1_rctr1_tdif</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Iset_rctr1_tdif</t>
         </is>
@@ -995,84 +1043,99 @@
         <v>10</v>
       </c>
       <c r="T2" s="2" t="n">
-        <v>36.75</v>
+        <v>35</v>
       </c>
       <c r="U2" s="2" t="n">
         <v>10.5</v>
       </c>
       <c r="V2" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="W2" s="2" t="n">
         <v>1000</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="X2" s="2" t="n">
         <v>5000</v>
       </c>
-      <c r="X2" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="Y2" s="2" t="n">
-        <v>1</v>
+        <v>5000</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AA2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" s="2" t="n">
+      <c r="AE2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AD2" s="2" t="n">
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AE2" s="2" t="n">
+      <c r="AJ2" s="2" t="n">
         <v>0.3</v>
-      </c>
-      <c r="AF2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AJ2" s="2" t="n">
-        <v>0.7</v>
       </c>
       <c r="AK2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AL2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN2" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AO2" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="AM2" s="2" t="n">
+      <c r="AR2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN2" s="2" t="n">
+      <c r="AS2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AO2" s="2" t="n">
+      <c r="AT2" s="2" t="n">
         <v>0.2</v>
       </c>
-      <c r="AP2" s="2" t="n">
+      <c r="AU2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AQ2" s="2" t="n">
+      <c r="AV2" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="AR2" s="2" t="n">
+      <c r="AW2" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="AS2" s="2" t="n">
+      <c r="AX2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AT2" s="2" t="n">
+      <c r="AY2" s="2" t="n">
         <v>1</v>
       </c>
     </row>

--- a/mode_docx_gen/pmi_dzt/kzt2_modes/КЦТ_1.xlsx
+++ b/mode_docx_gen/pmi_dzt/kzt2_modes/КЦТ_1.xlsx
@@ -985,59 +985,59 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>1</v>
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>1</v>
+        <v>0.02</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>5</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>1</v>
+        <v>0.02</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>5</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
       <c r="Q2" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.02</v>
       </c>
       <c r="S2" s="2" t="n">
         <v>10</v>
@@ -1052,13 +1052,13 @@
         <v>10.5</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>1</v>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AD2" s="2" t="n">
         <v>5</v>
@@ -1084,17 +1084,17 @@
       <c r="AG2" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
+      <c r="AH2" s="2" t="n">
+        <v>6</v>
       </c>
       <c r="AI2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AL2" s="2" t="n">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>1</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR2" s="2" t="n">
         <v>0.5</v>
@@ -1136,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="AY2" s="2" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>
@@ -1411,19 +1411,19 @@
         <v>0</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="X2" s="2" t="n">
         <v>240</v>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z2" s="2" t="n">
         <v>120</v>
@@ -2340,32 +2340,32 @@
       </c>
       <c r="BY2" s="2" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="BZ2" s="2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="CA2" s="2" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CB2" s="2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="CC2" s="2" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="CD2" s="2" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>0.55</t>
         </is>
       </c>
     </row>
